--- a/MIB_components.xlsx
+++ b/MIB_components.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arian\Documents\RAMMP\repos\RAMMP-Electronics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09CA538C-D261-4376-8DC6-742ADD7F7C93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E25266B-BA61-4D0E-AE3C-70C929B8A040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="0" windowWidth="14610" windowHeight="7845" activeTab="1" xr2:uid="{6F4A9416-ED2C-4136-AA62-A972BF68C866}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{6F4A9416-ED2C-4136-AA62-A972BF68C866}"/>
   </bookViews>
   <sheets>
     <sheet name="ICs" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="137">
   <si>
     <t>Digikey link</t>
   </si>
@@ -153,24 +153,6 @@
     <t>https://jlcpcb.com/partdetail/TexasInstruments-SN74LVC1G125DBVR/C23654</t>
   </si>
   <si>
-    <t>399-C0603C104K5RACTUCT-ND - Cut Tape</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/kemet/C0603C104K5RACTU/1465594</t>
-  </si>
-  <si>
-    <t>CAP CER 0.1UF 50V X7R 0603</t>
-  </si>
-  <si>
-    <t>C0603C104K5RACTU</t>
-  </si>
-  <si>
-    <t>https://jlcpcb.com/partdetail/KEMET-C0603C104K5RACTU/C127833</t>
-  </si>
-  <si>
-    <t>C127833</t>
-  </si>
-  <si>
     <t>CAP CER 0.047UF 50V X7R 0603</t>
   </si>
   <si>
@@ -207,9 +189,6 @@
     <t>C3994751</t>
   </si>
   <si>
-    <t>decoupling</t>
-  </si>
-  <si>
     <t>Loadcells</t>
   </si>
   <si>
@@ -339,27 +318,6 @@
     <t>C293663</t>
   </si>
   <si>
-    <t>https://www.digikey.com/en/products/detail/hirose-electric-co-ltd/DF1EC-3P-2-5DSA-35/5416401</t>
-  </si>
-  <si>
-    <t>H125165-ND</t>
-  </si>
-  <si>
-    <t>DF1EC-3P-2.5DSA(35)</t>
-  </si>
-  <si>
-    <t>CONN HEADER VERT 3POS 2.5MM</t>
-  </si>
-  <si>
-    <t>Roboclaws</t>
-  </si>
-  <si>
-    <t>https://jlcpcb.com/partdetail/HRS_Hirose-DF1EC_3P_2_5DSA_35/C720034</t>
-  </si>
-  <si>
-    <t>C720034</t>
-  </si>
-  <si>
     <t xml:space="preserve"> load cells</t>
   </si>
   <si>
@@ -460,6 +418,45 @@
   </si>
   <si>
     <t>3V3 and 5V decoup cap</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/molex/0901361103/760927</t>
+  </si>
+  <si>
+    <t>roboclaws</t>
+  </si>
+  <si>
+    <t>WM8214-ND</t>
+  </si>
+  <si>
+    <t>https://jlcpcb.com/partdetail/MOLEX-901361103/C588704</t>
+  </si>
+  <si>
+    <t>C588704</t>
+  </si>
+  <si>
+    <t>IMU and booster</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/murata-electronics/GCM155R71H104KE02D/4903704</t>
+  </si>
+  <si>
+    <t>490-10672-1-ND</t>
+  </si>
+  <si>
+    <t>CAP CER 0.1UF 50V X7R 0402</t>
+  </si>
+  <si>
+    <t>decoup</t>
+  </si>
+  <si>
+    <t>https://jlcpcb.com/partdetail/MurataElectronics-GCM155R71H104KE02D/C85858</t>
+  </si>
+  <si>
+    <t>C85858</t>
+  </si>
+  <si>
+    <t>GCM155R71H104KE02D</t>
   </si>
 </sst>
 </file>
@@ -901,7 +898,7 @@
         <v>4</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>10</v>
@@ -931,7 +928,7 @@
         <v>9</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>11</v>
@@ -1201,7 +1198,7 @@
         <v>4</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>10</v>
@@ -1211,30 +1208,30 @@
       </c>
       <c r="J1" s="3"/>
     </row>
-    <row r="2" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>35</v>
+        <v>131</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>37</v>
+        <v>132</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>53</v>
+        <v>133</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>39</v>
+        <v>134</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>40</v>
+        <v>135</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>38</v>
+        <v>136</v>
       </c>
       <c r="I2" s="1">
         <v>16</v>
@@ -1242,28 +1239,28 @@
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="I3" s="1">
         <v>2</v>
@@ -1271,28 +1268,28 @@
     </row>
     <row r="4" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="I4" s="1">
         <v>4</v>
@@ -1300,28 +1297,28 @@
     </row>
     <row r="5" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="I5" s="1">
         <v>4</v>
@@ -1329,28 +1326,28 @@
     </row>
     <row r="6" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="I6" s="1">
         <v>4</v>
@@ -1358,28 +1355,28 @@
     </row>
     <row r="7" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="I7" s="1">
         <v>4</v>
@@ -1387,28 +1384,28 @@
     </row>
     <row r="8" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="I8" s="1">
         <v>2</v>
@@ -1416,28 +1413,28 @@
     </row>
     <row r="9" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="I9" s="1">
         <v>2</v>
@@ -1642,21 +1639,21 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{0090FAA0-1F59-4169-AB66-911D7C8D11D4}"/>
-    <hyperlink ref="E2" r:id="rId2" xr:uid="{8B8C5B2D-224B-4187-906C-CFC6940B9E98}"/>
-    <hyperlink ref="A3" r:id="rId3" xr:uid="{5E88A924-6CAE-45C9-9C61-5482235674C9}"/>
-    <hyperlink ref="E3" r:id="rId4" xr:uid="{E8F6EB05-A4DB-4262-B73F-B733D414D55E}"/>
-    <hyperlink ref="A4" r:id="rId5" xr:uid="{796BD102-993C-4152-AE7E-5BE06141F742}"/>
-    <hyperlink ref="E4" r:id="rId6" xr:uid="{9CFB4CBA-C166-4B88-9EBF-A2BA7C8F2CC4}"/>
-    <hyperlink ref="E5" r:id="rId7" xr:uid="{7E8F88A3-CA09-4113-8FBB-40C143262C04}"/>
-    <hyperlink ref="A7" r:id="rId8" xr:uid="{45DBCD9B-42DF-4D8D-8F2F-90B96EDDBE07}"/>
-    <hyperlink ref="A6" r:id="rId9" xr:uid="{3234AFAB-194D-4FF1-8B89-BC35D190715C}"/>
-    <hyperlink ref="E6" r:id="rId10" xr:uid="{8302C569-81AF-47B6-B18A-D715B9F07856}"/>
-    <hyperlink ref="A5" r:id="rId11" xr:uid="{650C877D-CB0E-42A4-9517-68EFFD3BF5A2}"/>
-    <hyperlink ref="A8" r:id="rId12" xr:uid="{05A7980E-0A3E-42D4-B37E-CDB7F7C95971}"/>
-    <hyperlink ref="E8" r:id="rId13" xr:uid="{14C05EC6-86E8-4A95-9720-7640ED7A9582}"/>
-    <hyperlink ref="A9" r:id="rId14" xr:uid="{9E452824-2262-4185-8E38-FDE6624CE633}"/>
-    <hyperlink ref="E9" r:id="rId15" xr:uid="{09571E5B-14E2-42AA-9571-CEB496934A59}"/>
+    <hyperlink ref="A3" r:id="rId1" xr:uid="{5E88A924-6CAE-45C9-9C61-5482235674C9}"/>
+    <hyperlink ref="E3" r:id="rId2" xr:uid="{E8F6EB05-A4DB-4262-B73F-B733D414D55E}"/>
+    <hyperlink ref="A4" r:id="rId3" xr:uid="{796BD102-993C-4152-AE7E-5BE06141F742}"/>
+    <hyperlink ref="E4" r:id="rId4" xr:uid="{9CFB4CBA-C166-4B88-9EBF-A2BA7C8F2CC4}"/>
+    <hyperlink ref="E5" r:id="rId5" xr:uid="{7E8F88A3-CA09-4113-8FBB-40C143262C04}"/>
+    <hyperlink ref="A7" r:id="rId6" xr:uid="{45DBCD9B-42DF-4D8D-8F2F-90B96EDDBE07}"/>
+    <hyperlink ref="A6" r:id="rId7" xr:uid="{3234AFAB-194D-4FF1-8B89-BC35D190715C}"/>
+    <hyperlink ref="E6" r:id="rId8" xr:uid="{8302C569-81AF-47B6-B18A-D715B9F07856}"/>
+    <hyperlink ref="A5" r:id="rId9" xr:uid="{650C877D-CB0E-42A4-9517-68EFFD3BF5A2}"/>
+    <hyperlink ref="A8" r:id="rId10" xr:uid="{05A7980E-0A3E-42D4-B37E-CDB7F7C95971}"/>
+    <hyperlink ref="E8" r:id="rId11" xr:uid="{14C05EC6-86E8-4A95-9720-7640ED7A9582}"/>
+    <hyperlink ref="A9" r:id="rId12" xr:uid="{9E452824-2262-4185-8E38-FDE6624CE633}"/>
+    <hyperlink ref="E9" r:id="rId13" xr:uid="{09571E5B-14E2-42AA-9571-CEB496934A59}"/>
+    <hyperlink ref="A2" r:id="rId14" xr:uid="{194271A3-418F-440B-832A-0A2C9D2F288C}"/>
+    <hyperlink ref="E2" r:id="rId15" xr:uid="{E4B14731-1D1F-4974-8086-BEBEE777FF97}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1697,7 +1694,7 @@
         <v>4</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>10</v>
@@ -1708,28 +1705,28 @@
     </row>
     <row r="2" spans="1:9" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="I2" s="1">
         <v>2</v>
@@ -1737,22 +1734,22 @@
     </row>
     <row r="3" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>14</v>
@@ -1766,22 +1763,22 @@
     </row>
     <row r="4" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>14</v>
@@ -1795,28 +1792,28 @@
     </row>
     <row r="5" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>99</v>
+      <c r="H5" s="1">
+        <v>901361103</v>
       </c>
       <c r="I5" s="1">
         <v>3</v>
@@ -1824,19 +1821,19 @@
     </row>
     <row r="6" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
@@ -1847,19 +1844,19 @@
     </row>
     <row r="7" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
@@ -1870,19 +1867,19 @@
     </row>
     <row r="8" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
@@ -1893,28 +1890,28 @@
     </row>
     <row r="9" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="I9" s="1">
         <v>6</v>
@@ -2126,13 +2123,13 @@
     <hyperlink ref="E3" r:id="rId4" xr:uid="{174B51E9-EE21-477D-9EBD-30FD8C466D57}"/>
     <hyperlink ref="A4" r:id="rId5" xr:uid="{665E0FF7-917D-4028-8501-E3E05416ABD1}"/>
     <hyperlink ref="E4" r:id="rId6" xr:uid="{F6BE0CF5-3519-47A1-8D96-2D4F8E144780}"/>
-    <hyperlink ref="A5" r:id="rId7" xr:uid="{30024928-281E-4703-B8A8-FB5B7118F278}"/>
-    <hyperlink ref="E5" r:id="rId8" xr:uid="{1EA6F8AA-0916-43B4-9C2F-CD49D15A9207}"/>
-    <hyperlink ref="A6" r:id="rId9" xr:uid="{875A0879-9433-4D7B-ADF7-6672E67FAD49}"/>
-    <hyperlink ref="A7" r:id="rId10" xr:uid="{6E71F41D-C060-4165-965F-EEB83F1EB0D9}"/>
-    <hyperlink ref="A8" r:id="rId11" xr:uid="{E0E0E517-C39A-4C79-A325-D223FD14F874}"/>
-    <hyperlink ref="A9" r:id="rId12" xr:uid="{DD371F84-993D-4F11-AB05-FDFF4DA2574A}"/>
-    <hyperlink ref="E9" r:id="rId13" xr:uid="{6E611C34-8F42-4147-9D8B-4CF8056DD5C4}"/>
+    <hyperlink ref="A6" r:id="rId7" xr:uid="{875A0879-9433-4D7B-ADF7-6672E67FAD49}"/>
+    <hyperlink ref="A7" r:id="rId8" xr:uid="{6E71F41D-C060-4165-965F-EEB83F1EB0D9}"/>
+    <hyperlink ref="A8" r:id="rId9" xr:uid="{E0E0E517-C39A-4C79-A325-D223FD14F874}"/>
+    <hyperlink ref="A9" r:id="rId10" xr:uid="{DD371F84-993D-4F11-AB05-FDFF4DA2574A}"/>
+    <hyperlink ref="E9" r:id="rId11" xr:uid="{6E611C34-8F42-4147-9D8B-4CF8056DD5C4}"/>
+    <hyperlink ref="A5" r:id="rId12" xr:uid="{E6782339-9B93-42DE-9EA4-0DF5517B1A93}"/>
+    <hyperlink ref="E5" r:id="rId13" xr:uid="{847FD37F-66F5-49B3-BF09-557DBE7680D6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/MIB_components.xlsx
+++ b/MIB_components.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arian\Documents\RAMMP\repos\RAMMP-Electronics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E25266B-BA61-4D0E-AE3C-70C929B8A040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{428DDCC4-4630-4A5B-929E-6F6C5B33DFB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{6F4A9416-ED2C-4136-AA62-A972BF68C866}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="136">
   <si>
     <t>Digikey link</t>
   </si>
@@ -58,27 +58,7 @@
     <t>JLC part #</t>
   </si>
   <si>
-    <t>https://jlcpcb.com/partdetail/TexasInstruments-INA118PB/C1346736</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/texas-instruments/INA118PB/300978?s=N4IgTCBcDaIJIDkCCBGFAOACgIRAXQF8g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">	
-INA118PB-ND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">	
-IC INST AMP 1 CIRCUIT 8DIP</t>
-  </si>
-  <si>
-    <t>C1346736</t>
-  </si>
-  <si>
     <t>Manufacturer  part #</t>
-  </si>
-  <si>
-    <t>INA118PB</t>
   </si>
   <si>
     <t>https://www.digikey.com/en/products/detail/texas-instruments/REF2033QDDCRQ1/15926650?s=N4IgTCBcDaIEoFEBiYAMBmdBFAIjgwnFgIwgC6AvkA</t>
@@ -234,9 +214,6 @@
     <t>In Stock?</t>
   </si>
   <si>
-    <t>Yes, only 8 left</t>
-  </si>
-  <si>
     <t>Yes (505 left)</t>
   </si>
   <si>
@@ -457,6 +434,24 @@
   </si>
   <si>
     <t>GCM155R71H104KE02D</t>
+  </si>
+  <si>
+    <t>https://jlcpcb.com/partdetail/TexasInstruments-INA118U2K5/C431293</t>
+  </si>
+  <si>
+    <t>IC INST AMP 1 CIRCUIT 8SOIC</t>
+  </si>
+  <si>
+    <t>296-26056-1-ND</t>
+  </si>
+  <si>
+    <t>INA118U/2K5</t>
+  </si>
+  <si>
+    <t>C431293</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/texas-instruments/INA118U-2K5/2254830?utm_source=chatgpt.com</t>
   </si>
 </sst>
 </file>
@@ -889,7 +884,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>3</v>
@@ -898,40 +893,40 @@
         <v>4</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J1" s="3"/>
     </row>
     <row r="2" spans="1:10" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>6</v>
+        <v>135</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>132</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>62</v>
-      </c>
       <c r="H2" s="1" t="s">
-        <v>11</v>
+        <v>133</v>
       </c>
       <c r="I2" s="1">
         <v>4</v>
@@ -940,28 +935,28 @@
     </row>
     <row r="3" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="G3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="I3" s="1">
         <v>1</v>
@@ -969,28 +964,28 @@
     </row>
     <row r="4" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I4" s="1">
         <v>1</v>
@@ -998,28 +993,28 @@
     </row>
     <row r="5" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="I5" s="1">
         <v>1</v>
@@ -1149,14 +1144,14 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" xr:uid="{DE32DAC0-DAAB-451D-8121-43B336EB7D31}"/>
-    <hyperlink ref="A2" r:id="rId2" xr:uid="{8E7B69A1-9F16-4CA2-AB60-1B446365ADBD}"/>
-    <hyperlink ref="A3" r:id="rId3" xr:uid="{AD15D0B3-2118-4C28-8A1B-1D076F6B097F}"/>
-    <hyperlink ref="E3" r:id="rId4" xr:uid="{B3C35203-B095-4B55-AAED-6CCED287487A}"/>
-    <hyperlink ref="A4" r:id="rId5" xr:uid="{1023CE1E-0313-4F6A-8A49-4B5FCFAA93EE}"/>
-    <hyperlink ref="A5" r:id="rId6" xr:uid="{DA8D95FB-13FB-4F7F-80F5-8E14E5F2BD50}"/>
-    <hyperlink ref="E5" r:id="rId7" xr:uid="{F163AD94-952E-4351-B375-AD123D63FC34}"/>
-    <hyperlink ref="E4" r:id="rId8" xr:uid="{B6C22098-5BA7-4AEF-AF4E-95C677DF4730}"/>
+    <hyperlink ref="A3" r:id="rId1" xr:uid="{AD15D0B3-2118-4C28-8A1B-1D076F6B097F}"/>
+    <hyperlink ref="E3" r:id="rId2" xr:uid="{B3C35203-B095-4B55-AAED-6CCED287487A}"/>
+    <hyperlink ref="A4" r:id="rId3" xr:uid="{1023CE1E-0313-4F6A-8A49-4B5FCFAA93EE}"/>
+    <hyperlink ref="A5" r:id="rId4" xr:uid="{DA8D95FB-13FB-4F7F-80F5-8E14E5F2BD50}"/>
+    <hyperlink ref="E5" r:id="rId5" xr:uid="{F163AD94-952E-4351-B375-AD123D63FC34}"/>
+    <hyperlink ref="E4" r:id="rId6" xr:uid="{B6C22098-5BA7-4AEF-AF4E-95C677DF4730}"/>
+    <hyperlink ref="E2" r:id="rId7" xr:uid="{49DEC857-9C8A-442E-8FE8-297977B0A3D9}"/>
+    <hyperlink ref="A2" r:id="rId8" xr:uid="{DA248814-7014-41D7-BE88-DC80E3297943}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId9"/>
@@ -1189,7 +1184,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>3</v>
@@ -1198,40 +1193,40 @@
         <v>4</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J1" s="3"/>
     </row>
     <row r="2" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="I2" s="1">
         <v>16</v>
@@ -1239,28 +1234,28 @@
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I3" s="1">
         <v>2</v>
@@ -1268,28 +1263,28 @@
     </row>
     <row r="4" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="I4" s="1">
         <v>4</v>
@@ -1297,28 +1292,28 @@
     </row>
     <row r="5" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="G5" s="1" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I5" s="1">
         <v>4</v>
@@ -1326,28 +1321,28 @@
     </row>
     <row r="6" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="I6" s="1">
         <v>4</v>
@@ -1355,28 +1350,28 @@
     </row>
     <row r="7" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="I7" s="1">
         <v>4</v>
@@ -1384,28 +1379,28 @@
     </row>
     <row r="8" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="I8" s="1">
         <v>2</v>
@@ -1413,28 +1408,28 @@
     </row>
     <row r="9" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="I9" s="1">
         <v>2</v>
@@ -1685,7 +1680,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>3</v>
@@ -1694,39 +1689,39 @@
         <v>4</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="I2" s="1">
         <v>2</v>
@@ -1734,25 +1729,25 @@
     </row>
     <row r="3" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H3" s="1">
         <v>705430004</v>
@@ -1763,25 +1758,25 @@
     </row>
     <row r="4" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H4" s="1">
         <v>705430003</v>
@@ -1792,25 +1787,25 @@
     </row>
     <row r="5" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H5" s="1">
         <v>901361103</v>
@@ -1821,19 +1816,19 @@
     </row>
     <row r="6" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
@@ -1844,19 +1839,19 @@
     </row>
     <row r="7" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
@@ -1867,19 +1862,19 @@
     </row>
     <row r="8" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
@@ -1890,28 +1885,28 @@
     </row>
     <row r="9" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="I9" s="1">
         <v>6</v>

--- a/MIB_components.xlsx
+++ b/MIB_components.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arian\Documents\RAMMP\repos\RAMMP-Electronics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{428DDCC4-4630-4A5B-929E-6F6C5B33DFB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA9D20F9-1E93-4824-A66F-427D62F26B0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{6F4A9416-ED2C-4136-AA62-A972BF68C866}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="ICs" sheetId="1" r:id="rId1"/>
     <sheet name="Resistors+capacitors+ferrite" sheetId="2" r:id="rId2"/>
     <sheet name="headers" sheetId="3" r:id="rId3"/>
+    <sheet name="Other" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="183">
   <si>
     <t>Digikey link</t>
   </si>
@@ -452,6 +453,147 @@
   </si>
   <si>
     <t>https://www.digikey.com/en/products/detail/texas-instruments/INA118U-2K5/2254830?utm_source=chatgpt.com</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/c-k/OS102011MS2QN1/411602</t>
+  </si>
+  <si>
+    <t>CKN9565-ND</t>
+  </si>
+  <si>
+    <t>SWITCH SLIDE SPDT 100MA 12V</t>
+  </si>
+  <si>
+    <t>switch for can termination ends</t>
+  </si>
+  <si>
+    <t>C221829</t>
+  </si>
+  <si>
+    <t>https://jlcpcb.com/partdetail/CK-OS102011MS2QN1/C221829</t>
+  </si>
+  <si>
+    <t>OS102011MS2QN1</t>
+  </si>
+  <si>
+    <t>enc rc filter</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/yageo/CC1206FKNPO9BN822/11491888</t>
+  </si>
+  <si>
+    <t>13-CC1206FKNPO9BN822CT-ND</t>
+  </si>
+  <si>
+    <t>CAP CER 8200PF 50V C0G/NPO 1206</t>
+  </si>
+  <si>
+    <t>https://jlcpcb.com/partdetail/YAGEO-CC1206FKNPO9BN822/C541598</t>
+  </si>
+  <si>
+    <t>C541598</t>
+  </si>
+  <si>
+    <t>CC1206FKNPO9BN822</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/yageo/SR2512FK-7W10RL/9373192</t>
+  </si>
+  <si>
+    <t>YAG5923CT-ND</t>
+  </si>
+  <si>
+    <t>RES 10 OHM 1% 2W 2512</t>
+  </si>
+  <si>
+    <t>https://jlcpcb.com/partdetail/YAGEO-SR2512FK7W10RL/C876843</t>
+  </si>
+  <si>
+    <t>C876843</t>
+  </si>
+  <si>
+    <t>SR2512FK-7W10RL</t>
+  </si>
+  <si>
+    <t>loadcell input filter</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/yageo/RT13-RT1206FRE075KLCT-ND1206FRE075KL/7708705</t>
+  </si>
+  <si>
+    <t>13-RT1206FRE075KLCT-ND</t>
+  </si>
+  <si>
+    <t>RES 5K OHM 1% 1/4W 1206</t>
+  </si>
+  <si>
+    <t>https://jlcpcb.com/partdetail/YAGEO-RT1206FRE075KL/C872846</t>
+  </si>
+  <si>
+    <t>C872846</t>
+  </si>
+  <si>
+    <t>Tes</t>
+  </si>
+  <si>
+    <t>RT1206FRE075KL</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/murata-electronics/GRM31C5C1H683JA01L/702624?s=N4IgTCBcDaIOICUCyBmAjAYQKwbQCQDYAOFAKQEEAGNAGRAF0BfIA</t>
+  </si>
+  <si>
+    <t>CAP CER 0.068UF 50V C0G/NP0 1206</t>
+  </si>
+  <si>
+    <t>490-3360-1-ND</t>
+  </si>
+  <si>
+    <t>https://jlcpcb.com/partdetail/MurataElectronics-GRM31C5C1H683JA01L/C77084</t>
+  </si>
+  <si>
+    <t>C77084</t>
+  </si>
+  <si>
+    <t>GRM31C5C1H683JA01L</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/murata-electronics/GRM2195C1H682JA01D/586783?s=N4IgTCBcDaIOICUCyYCMBOArAYVQCQDYAOMAKQEEAGVAERAF0BfIA</t>
+  </si>
+  <si>
+    <t>490-1638-1-ND</t>
+  </si>
+  <si>
+    <t>CAP CER 6800PF 50V C0G/NP0 0805</t>
+  </si>
+  <si>
+    <t>https://jlcpcb.com/partdetail/MurataElectronics-GRM2195C1H682JA01D/C77068</t>
+  </si>
+  <si>
+    <t>C77068</t>
+  </si>
+  <si>
+    <t>GRM2195C1H682JA01D</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/yageo/RC0603FR-07931RL/727433?s=N4IgTCBcDaIEoGEAMA2JBmAYnAtEg7AJzoCMcAMiALoC%2BQA</t>
+  </si>
+  <si>
+    <t>311-931HRCT-ND</t>
+  </si>
+  <si>
+    <t>RES 931 OHM 1% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>loadcell rg</t>
+  </si>
+  <si>
+    <t>https://jlcpcb.com/partdetail/YAGEO-RC0603FR07931RL/C163416</t>
+  </si>
+  <si>
+    <t>C163416</t>
+  </si>
+  <si>
+    <t>RC0603FR-07931RL</t>
   </si>
 </sst>
 </file>
@@ -1435,71 +1577,179 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="2"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="2"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="2"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
+    <row r="10" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="I10" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="I11" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="I12" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="I13" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="I14" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="I15" s="1">
+        <v>4</v>
+      </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B16" s="1"/>
@@ -1649,6 +1899,13 @@
     <hyperlink ref="E9" r:id="rId13" xr:uid="{09571E5B-14E2-42AA-9571-CEB496934A59}"/>
     <hyperlink ref="A2" r:id="rId14" xr:uid="{194271A3-418F-440B-832A-0A2C9D2F288C}"/>
     <hyperlink ref="E2" r:id="rId15" xr:uid="{E4B14731-1D1F-4974-8086-BEBEE777FF97}"/>
+    <hyperlink ref="A10" r:id="rId16" xr:uid="{76FB30C6-FCC1-4C98-A51E-CAAC4A84BD65}"/>
+    <hyperlink ref="A12" r:id="rId17" xr:uid="{2C31FDAB-A0F7-4387-B752-FB26F26BE9BE}"/>
+    <hyperlink ref="E12" r:id="rId18" xr:uid="{F3C995A3-C938-40E8-BFD4-68215BCC5E7F}"/>
+    <hyperlink ref="A14" r:id="rId19" xr:uid="{AA7EAD3A-A4FD-40C3-AB07-18168BC2E35A}"/>
+    <hyperlink ref="E14" r:id="rId20" xr:uid="{E9B51828-3DD6-465C-965B-6E0FE0472F88}"/>
+    <hyperlink ref="A13" r:id="rId21" xr:uid="{CA7F45DC-B8C4-48FF-AD50-773966E9CA67}"/>
+    <hyperlink ref="A15" r:id="rId22" xr:uid="{AD6D9115-CCB9-446E-B796-FAE0077DC687}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2128,4 +2385,272 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63E81612-F72A-446E-88F7-33413BF829AC}">
+  <dimension ref="A1:I19"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="32.5546875" customWidth="1"/>
+    <col min="2" max="2" width="14.5546875" customWidth="1"/>
+    <col min="3" max="3" width="19.21875" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="31.44140625" customWidth="1"/>
+    <col min="8" max="8" width="18.77734375" customWidth="1"/>
+    <col min="9" max="9" width="13.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I2" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{495BC442-A473-4A63-8A52-76B4B9CEAF2E}"/>
+    <hyperlink ref="E2" r:id="rId2" xr:uid="{348AC21B-3EFA-4731-B349-2709FFAF7AC3}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/MIB_components.xlsx
+++ b/MIB_components.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arian\Documents\RAMMP\repos\RAMMP-Electronics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA9D20F9-1E93-4824-A66F-427D62F26B0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43C9D527-259A-4D70-BBF0-56DB908E81E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{6F4A9416-ED2C-4136-AA62-A972BF68C866}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{6F4A9416-ED2C-4136-AA62-A972BF68C866}"/>
   </bookViews>
   <sheets>
     <sheet name="ICs" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="189">
   <si>
     <t>Digikey link</t>
   </si>
@@ -594,6 +594,24 @@
   </si>
   <si>
     <t>RC0603FR-07931RL</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/keystone-electronics/5003/362668</t>
+  </si>
+  <si>
+    <t>36-5003-ND</t>
+  </si>
+  <si>
+    <t>PC TEST POINT MINIATURE ORANGE</t>
+  </si>
+  <si>
+    <t>Test points</t>
+  </si>
+  <si>
+    <t>https://jlcpcb.com/partdetail/Keystone-5003/C238124?jlc_vid=ElFbA10EEwBaVQECRAILXlEDFVkLVVNXFgcLBlVfQFgxVlNeQFJcU1xRRlddVjtW</t>
+  </si>
+  <si>
+    <t>C238124</t>
   </si>
 </sst>
 </file>
@@ -2392,11 +2410,12 @@
   <dimension ref="A1:I19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.5546875" customWidth="1"/>
+    <col min="1" max="1" width="41" customWidth="1"/>
     <col min="2" max="2" width="14.5546875" customWidth="1"/>
     <col min="3" max="3" width="19.21875" customWidth="1"/>
     <col min="4" max="4" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="31.44140625" customWidth="1"/>
+    <col min="5" max="5" width="39" customWidth="1"/>
+    <col min="6" max="6" width="38.44140625" customWidth="1"/>
     <col min="8" max="8" width="18.77734375" customWidth="1"/>
     <col min="9" max="9" width="13.88671875" customWidth="1"/>
   </cols>
@@ -2459,15 +2478,31 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
+    <row r="3" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="1">
+        <v>5003</v>
+      </c>
       <c r="I3" s="1"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -2650,6 +2685,8 @@
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{495BC442-A473-4A63-8A52-76B4B9CEAF2E}"/>
     <hyperlink ref="E2" r:id="rId2" xr:uid="{348AC21B-3EFA-4731-B349-2709FFAF7AC3}"/>
+    <hyperlink ref="A3" r:id="rId3" xr:uid="{B96DC06A-F590-45DF-A2D7-35C2456E0208}"/>
+    <hyperlink ref="E3" r:id="rId4" xr:uid="{4BAF805E-1312-4972-AB0E-B1C6E6C71183}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
